--- a/Rift_Protocol_Card_Reference.xlsx
+++ b/Rift_Protocol_Card_Reference.xlsx
@@ -945,7 +945,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Junction Fire: your attacks deal [DMG +1]; Burn 2.</t>
+          <t>Junction Fire: your attacks deal +1; Burn 2.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, twice.</t>
+          <t>Deal 3 to one enemy, twice.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy, Pierce.</t>
+          <t>Deal 5 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on a fighter.</t>
+          <t>Block 10 on a fighter.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on a fighter.</t>
+          <t>Block 10 on a fighter.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Guard [BLK 1] on this fighter.</t>
+          <t>Guard 1 on this fighter.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on both fighters.</t>
+          <t>Guard 2 on both fighters.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, three times.</t>
+          <t>Deal 3 to one enemy, three times.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Burn 2.</t>
+          <t>Deal 3 to one enemy; Burn 2.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Burn 2.</t>
+          <t>Deal 3 to one enemy; Burn 2.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Deal [DMG 9] to one enemy; [DMG 3] to the other enemy.</t>
+          <t>Deal 9 to one enemy; 3 to the other enemy.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to both enemies.</t>
+          <t>Deal 5 to both enemies.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Block [BLK 8].</t>
+          <t>Block 8.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Block [BLK 4]; Riposte 4.</t>
+          <t>Block 4; Riposte 4.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Guard [BLK 4] on this fighter.</t>
+          <t>Guard 4 on this fighter.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on a fighter.</t>
+          <t>Guard 3 on a fighter.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Next turn: enemy team has [NRG 2] less energy.</t>
+          <t>Next turn: enemy team has 2 less energy.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Heal [HEAL 3] to this fighter.</t>
+          <t>Deal 3 to one enemy; Heal 3 to this fighter.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Deal [DMG 8] to both enemies, Pierce.</t>
+          <t>Deal 8 to both enemies, Pierce.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; [DMG +1] if you also attack it or it took damage.</t>
+          <t>Deal 3 to one enemy; +1 if you also attack it or it took damage.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Guard [BLK 4] on this fighter.</t>
+          <t>Guard 4 on this fighter.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on both fighters.</t>
+          <t>Guard 3 on both fighters.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Block [BLK 3]; Riposte 4 (first only).</t>
+          <t>Block 3; Riposte 4 (first only).</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; this fighter then ignores all damage.</t>
+          <t>Deal 4 to one enemy; this fighter then ignores all damage.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Flip: Deal [DMG 7] Heads, [DMG 4] Tails to one enemy.</t>
+          <t>Flip: Deal 7 Heads, 4 Tails to one enemy.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Deal [DMG 9] to one enemy.</t>
+          <t>Deal 9 to one enemy.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to both enemies.</t>
+          <t>Deal 5 to both enemies.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Guard [BLK 5] on this fighter.</t>
+          <t>Guard 5 on this fighter.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Block [BLK 7].</t>
+          <t>Block 7.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter; Expose 1 next turn.</t>
+          <t>Heal 4 to a fighter; Expose 1 next turn.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Discard a card: draw [DRAW 2] extra next turn.</t>
+          <t>Discard a card: draw 2 extra next turn.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Deal [DMG 8] to one enemy; [DMG 10] if this fighter is below half HP.</t>
+          <t>Deal 8 to one enemy; 10 if this fighter is below half HP.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, Pierce.</t>
+          <t>Deal 3 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Deal [DMG 7] to one enemy.</t>
+          <t>Deal 7 to one enemy.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Block [BLK 9] on a fighter.</t>
+          <t>Block 9 on a fighter.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Heal [HEAL 2] to a fighter, now and next turn.</t>
+          <t>Heal 2 to a fighter, now and next turn.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on a fighter.</t>
+          <t>Guard 3 on a fighter.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Heal [HEAL 1] to both fighters; Guard [BLK 1].</t>
+          <t>Heal 1 to both fighters; Guard 1.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Move up to [HEAL 6] from the healthier fighter to the weaker.</t>
+          <t>Move up to 6 HP from the healthier fighter to the weaker.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Heal [HEAL 6] to a fighter.</t>
+          <t>Heal 6 to a fighter.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on both fighters (stops Pierce).</t>
+          <t>Block 10 on both fighters (stops Pierce).</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; Weaken 2 next turn.</t>
+          <t>Deal 4 to one enemy; Weaken 2 next turn.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Deal [DMG 7] to one enemy.</t>
+          <t>Deal 7 to one enemy.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Deal [DMG 2] to both enemies.</t>
+          <t>Deal 2 to both enemies.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Block [BLK 6]; Riposte 3.</t>
+          <t>Block 6; Riposte 3.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Block [BLK 6]; Riposte 3.</t>
+          <t>Block 6; Riposte 3.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Block [BLK 6] on both fighters.</t>
+          <t>Block 6 on both fighters.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Heal [HEAL 5] to a fighter.</t>
+          <t>Heal 5 to a fighter.</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on this fighter.</t>
+          <t>Guard 2 on this fighter.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>First time this fighter's Block overflows, Block [BLK 2] more.</t>
+          <t>First time this fighter's Block overflows, Block 2 more.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on both fighters.</t>
+          <t>Guard 2 on both fighters.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; Block [BLK 8] next turn.</t>
+          <t>Deal 4 to one enemy; Block 8 next turn.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Junction Fire: your attacks deal [DMG +1]; Burn 2.</t>
+          <t>Junction Fire: your attacks deal +1; Burn 2.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, twice.</t>
+          <t>Deal 3 to one enemy, twice.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy, Pierce.</t>
+          <t>Deal 5 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on a fighter.</t>
+          <t>Block 10 on a fighter.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on a fighter.</t>
+          <t>Block 10 on a fighter.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Guard [BLK 1] on this fighter.</t>
+          <t>Guard 1 on this fighter.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on both fighters.</t>
+          <t>Guard 2 on both fighters.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, three times.</t>
+          <t>Deal 3 to one enemy, three times.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Burn 2.</t>
+          <t>Deal 3 to one enemy; Burn 2.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Burn 2.</t>
+          <t>Deal 3 to one enemy; Burn 2.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 9] to one enemy; [DMG 3] to the other enemy.</t>
+          <t>Deal 9 to one enemy; 3 to the other enemy.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to both enemies.</t>
+          <t>Deal 5 to both enemies.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Block [BLK 8].</t>
+          <t>Block 8.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Block [BLK 4]; Riposte 4.</t>
+          <t>Block 4; Riposte 4.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Guard [BLK 4] on this fighter.</t>
+          <t>Guard 4 on this fighter.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on a fighter.</t>
+          <t>Guard 3 on a fighter.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Next turn: enemy team has [NRG 2] less energy.</t>
+          <t>Next turn: enemy team has 2 less energy.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; Heal [HEAL 3] to this fighter.</t>
+          <t>Deal 3 to one enemy; Heal 3 to this fighter.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 8] to both enemies, Pierce.</t>
+          <t>Deal 8 to both enemies, Pierce.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy; [DMG +1] if you also attack it or it took damage.</t>
+          <t>Deal 3 to one enemy; +1 if you also attack it or it took damage.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Guard [BLK 4] on this fighter.</t>
+          <t>Guard 4 on this fighter.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on both fighters.</t>
+          <t>Guard 3 on both fighters.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 3]; Riposte 4 (first only).</t>
+          <t>Block 3; Riposte 4 (first only).</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; this fighter then ignores all damage.</t>
+          <t>Deal 4 to one enemy; this fighter then ignores all damage.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deal [DMG 6] to one enemy.</t>
+          <t>Deal 6 to one enemy.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Flip: Deal [DMG 7] Heads, [DMG 4] Tails to one enemy.</t>
+          <t>Flip: Deal 7 Heads, 4 Tails to one enemy.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 9] to one enemy.</t>
+          <t>Deal 9 to one enemy.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to both enemies.</t>
+          <t>Deal 5 to both enemies.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Guard [BLK 5] on this fighter.</t>
+          <t>Guard 5 on this fighter.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 7].</t>
+          <t>Block 7.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter; Expose 1 next turn.</t>
+          <t>Heal 4 to a fighter; Expose 1 next turn.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Discard a card: draw [DRAW 2] extra next turn.</t>
+          <t>Discard a card: draw 2 extra next turn.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 8] to one enemy; [DMG 10] if this fighter is below half HP.</t>
+          <t>Deal 8 to one enemy; 10 if this fighter is below half HP.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy, Pierce.</t>
+          <t>Deal 3 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 7] to one enemy.</t>
+          <t>Deal 7 to one enemy.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to both enemies.</t>
+          <t>Deal 3 to both enemies.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Heal [HEAL 4] to a fighter.</t>
+          <t>Heal 4 to a fighter.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Deal [DMG 3] to one enemy.</t>
+          <t>Deal 3 to one enemy.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Block [BLK 9] on a fighter.</t>
+          <t>Block 9 on a fighter.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Heal [HEAL 2] to a fighter, now and next turn.</t>
+          <t>Heal 2 to a fighter, now and next turn.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Guard [BLK 3] on a fighter.</t>
+          <t>Guard 3 on a fighter.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Heal [HEAL 1] to both fighters; Guard [BLK 1].</t>
+          <t>Heal 1 to both fighters; Guard 1.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Move up to [HEAL 6] from the healthier fighter to the weaker.</t>
+          <t>Move up to 6 HP from the healthier fighter to the weaker.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 6] to a fighter.</t>
+          <t>Heal 6 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Block [BLK 10] on both fighters (stops Pierce).</t>
+          <t>Block 10 on both fighters (stops Pierce).</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deal [DMG 5] to one enemy.</t>
+          <t>Deal 5 to one enemy.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy.</t>
+          <t>Deal 4 to one enemy.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; Weaken 2 next turn.</t>
+          <t>Deal 4 to one enemy; Weaken 2 next turn.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy, Pierce.</t>
+          <t>Deal 4 to one enemy, Pierce.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deal [DMG 7] to one enemy.</t>
+          <t>Deal 7 to one enemy.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deal [DMG 2] to both enemies.</t>
+          <t>Deal 2 to both enemies.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Block [BLK 6]; Riposte 3.</t>
+          <t>Block 6; Riposte 3.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Block [BLK 6]; Riposte 3.</t>
+          <t>Block 6; Riposte 3.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Block [BLK 6] on both fighters.</t>
+          <t>Block 6 on both fighters.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Block [BLK 5]; Riposte 4.</t>
+          <t>Block 5; Riposte 4.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Heal [HEAL 5] to a fighter.</t>
+          <t>Heal 5 to a fighter.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on this fighter.</t>
+          <t>Guard 2 on this fighter.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>First time this fighter's Block overflows, Block [BLK 2] more.</t>
+          <t>First time this fighter's Block overflows, Block 2 more.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Guard [BLK 2] on both fighters.</t>
+          <t>Guard 2 on both fighters.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Heal [HEAL 8] to a fighter.</t>
+          <t>Heal 8 to a fighter.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deal [DMG 4] to one enemy; Block [BLK 8] next turn.</t>
+          <t>Deal 4 to one enemy; Block 8 next turn.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/Rift_Protocol_Card_Reference.xlsx
+++ b/Rift_Protocol_Card_Reference.xlsx
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Disrupt</t>
+          <t>Flash Bang</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3345,14 +3345,17 @@
           <t>enemy</t>
         </is>
       </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>One enemy's T4 attack resolves at T3.</t>
+          <t>Weaken 3 on one enemy.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Knock the timing off.</t>
+          <t>A white flash, and their aim is gone.</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8724,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Disrupt</t>
+          <t>Flash Bang</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8742,14 +8745,17 @@
           <t>enemy</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>One enemy's T4 attack resolves at T3.</t>
+          <t>Weaken 3 on one enemy.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Knock the timing off.</t>
+          <t>A white flash, and their aim is gone.</t>
         </is>
       </c>
     </row>
